--- a/Output/gls_model_interruption2_weekly_output.xlsx
+++ b/Output/gls_model_interruption2_weekly_output.xlsx
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
